--- a/02-PROFESORADO/05-ECOSISTEMA-DIGITAL/PLANTILLAS-MAESTRAS/02-Scrum-equipo-MiniJarvis.xlsx
+++ b/02-PROFESORADO/05-ECOSISTEMA-DIGITAL/PLANTILLAS-MAESTRAS/02-Scrum-equipo-MiniJarvis.xlsx
@@ -8,25 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EQUIPO_Y_ACUERDOS" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PRODUCT_BACKLOG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRINT_ACTUAL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DECISIONES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BLOQUEOS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETROSPECTIVAS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REGISTRO_IA_EQUIPO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENLACES_EVIDENCIAS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BACKLOG_OPERATIVO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DECISIONES_Y_BLOQUEOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REVIEW" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RETROSPECTIVA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IA_EQUIPO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EQUIPO_Y_ACUERDOS'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PRODUCT_BACKLOG'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SPRINT_ACTUAL'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DECISIONES'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BLOQUEOS'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'REVIEW'!$A$1:$H$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'RETROSPECTIVAS'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'REGISTRO_IA_EQUIPO'!$A$1:$I$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'ENLACES_EVIDENCIAS'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'EQUIPO_Y_ACUERDOS'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BACKLOG_OPERATIVO'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DECISIONES_Y_BLOQUEOS'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REVIEW'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'RETROSPECTIVA'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IA_EQUIPO'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'INSTRUCCIONES'!$A$1:$B$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -57,7 +53,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="002457A6"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,13 +69,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,14 +439,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,33 +472,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Sustitución prevista</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Rotación prevista</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -516,17 +488,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,47 +540,17 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>URL evidencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Inicio / fin</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Enlace si aporta valor</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Pendiente,En curso,Hecho,Bloqueado"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,98 +561,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID backlog</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Tarea</t>
+          <t>Hito</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Alternativas / impacto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Acción o motivo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Inicio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Fin previsto</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Bloqueo</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Enlace si aporta valor</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Pendiente,En curso,Hecho,Bloqueado"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -720,16 +634,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,59 +660,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Decisión</t>
+          <t>Incremento mostrado</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Alternativas</t>
+          <t>Prueba</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Motivo</t>
+          <t>Resultado</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Quién participó</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>URL evidencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Siguiente cambio</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Enlace</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -808,16 +701,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,17 +726,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Bloqueo</t>
+          <t>Qué salió bien</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Impacto</t>
+          <t>Qué mejorar</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Acción</t>
+          <t>Acción concreta</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -853,44 +746,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Fecha de revisión</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
-  <dataValidations count="1">
-    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Pendiente,En curso,Hecho,Bloqueado"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -901,17 +762,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -927,67 +788,37 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Incremento mostrado</t>
+          <t>Herramienta</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Prueba</t>
+          <t>Finalidad / entrada resumida</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Resultado usado</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Validación humana</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Siguiente cambio</t>
+          <t>Responsable</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>Enlace</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -998,278 +829,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fecha</t>
+          <t>Regla</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Hito</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Qué salió bien</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Qué mejorar</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Acción concreta</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha revisión</t>
+          <t>Aplicación</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cuándo actualizar</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nueva tarea, cambio de estado, decisión, bloqueo, review, retrospectiva o IA colectiva significativa; nunca por cuota de sesión.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Enlaces estables</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Se registran una vez fuera de esta hoja; no se repiten por evidencia.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Review / retrospectiva</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Review comprueba el producto; retrospectiva mejora el proceso.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Hito</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Herramienta</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Finalidad</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt resumido</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado usado</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Validación</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Responsable</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hito</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>URL profunda</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Permiso comprobado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Versión/fecha</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Exportación cerrada</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:B4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>